--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484162_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484162_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3148</v>
+        <v>4.6232</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0355</v>
+        <v>4.7345</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2793</v>
+        <v>-0.1113</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1772</v>
+        <v>2.1075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1511</v>
+        <v>2.3485</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0261</v>
+        <v>-0.241</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9707</v>
+        <v>4.534</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6855</v>
+        <v>4.4058</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2852</v>
+        <v>0.1281</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7935</v>
+        <v>-2.4264</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5344</v>
+        <v>-2.0573</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2591</v>
+        <v>-0.3691</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3968</v>
+        <v>2.9758</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7935</v>
+        <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8599</v>
+        <v>-0.1941</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2551</v>
+        <v>-0.4703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6047</v>
+        <v>0.2762</v>
       </c>
       <c r="V2" t="n">
-        <v>1.881</v>
+        <v>-0.266</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6745</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1151</v>
+        <v>4.3094</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4228</v>
+        <v>3.0581</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3077</v>
+        <v>1.2513</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1075</v>
+        <v>1.1772</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3485</v>
+        <v>0.1511</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.241</v>
+        <v>1.0261</v>
       </c>
       <c r="J3" t="n">
-        <v>4.534</v>
+        <v>1.9707</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4058</v>
+        <v>0.6855</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1281</v>
+        <v>1.2852</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.4264</v>
+        <v>-0.7935</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0573</v>
+        <v>-0.5344</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3691</v>
+        <v>-0.2591</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9758</v>
+        <v>0.3968</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1741</v>
+        <v>0.7935</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7023</v>
+        <v>0.8545</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.782</v>
+        <v>0.2778</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0798</v>
+        <v>0.5767</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.266</v>
+        <v>1.881</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1352</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9747</v>
+        <v>2.9626</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8782</v>
+        <v>2.4733</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0965</v>
+        <v>0.4892</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1499</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4272</v>
+        <v>-0.4393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8388</v>
+        <v>-0.2436</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5884</v>
+        <v>-0.1957</v>
       </c>
       <c r="V4" t="n">
         <v>3.3534</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4321</v>
+        <v>1.8818</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4968</v>
+        <v>1.5818</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
         <v>1.0404</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2872</v>
+        <v>-0.8375</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.544</v>
+        <v>-0.459</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7432</v>
+        <v>-0.3785</v>
       </c>
       <c r="V5" t="n">
         <v>2.0757</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4469</v>
+        <v>1.3662</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5724</v>
+        <v>-0.1019</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0193</v>
+        <v>1.4682</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5666</v>
@@ -922,13 +922,13 @@
         <v>2.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5655</v>
+        <v>-0.6461</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9748</v>
+        <v>-0.5044</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5907</v>
+        <v>-0.1418</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -951,13 +951,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4469</v>
+        <v>1.3662</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5724</v>
+        <v>-0.1019</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0193</v>
+        <v>1.4682</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5666</v>
@@ -996,13 +996,13 @@
         <v>2.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5655</v>
+        <v>-0.6461</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9748</v>
+        <v>-0.5044</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5907</v>
+        <v>-0.1418</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,73 +1029,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.915</v>
+        <v>-2.0024</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1964</v>
+        <v>-1.8885</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7186</v>
+        <v>-0.1139</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.753</v>
+        <v>-2.1427</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.21</v>
+        <v>-1.0584</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5431</v>
+        <v>-1.0844</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.1054</v>
+        <v>-0.5395</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3526</v>
+        <v>-0.66</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7529</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6476</v>
+        <v>-1.6032</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.3983</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7902</v>
+        <v>-1.2048</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.5952</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.3887</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.7935</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.3968</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1903</v>
-      </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>0.3982</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8333</v>
+        <v>0.0397</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5367</v>
+        <v>0.3585</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6745</v>
+        <v>0.3373</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,73 +1107,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9511</v>
+        <v>-2.5864</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8091</v>
+        <v>-1.5592</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.142</v>
+        <v>-1.0272</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1427</v>
+        <v>-4.753</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0584</v>
+        <v>-3.21</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0844</v>
+        <v>-1.5431</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5395</v>
+        <v>-3.1054</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.66</v>
+        <v>-2.3526</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>-0.7529</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6032</v>
+        <v>-1.6476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3983</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2048</v>
+        <v>-0.7902</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4495</v>
+        <v>0.6986</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1191</v>
+        <v>0.4705</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3304</v>
+        <v>0.228</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3373</v>
+        <v>0.6745</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3373</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,73 +1185,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.315</v>
+        <v>-2.6098</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1717</v>
+        <v>0.2268</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1433</v>
+        <v>-2.8366</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1319</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5295</v>
+        <v>-0.1312</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6024</v>
+        <v>-0.4016</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1319</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5295</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6024</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.1312</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S10" t="n">
-        <v>1.553</v>
+        <v>0.3359</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6802</v>
+        <v>0.4251</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8728</v>
+        <v>-0.0893</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.0162</v>
+        <v>-2.4129</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.0162</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1263,67 +1263,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4338</v>
+        <v>-3.0972</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4308</v>
+        <v>-0.5798</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8646</v>
+        <v>-2.5174</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5328000000000001</v>
+        <v>1.1319</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1312</v>
+        <v>0.5295</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4016</v>
+        <v>0.6024</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.1319</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.5295</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.6024</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1312</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5119</v>
+        <v>0.7708</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6292</v>
+        <v>0.2721</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1173</v>
+        <v>0.4988</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4129</v>
+        <v>-3.0162</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4129</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="12">
@@ -1341,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8362</v>
+        <v>-3.5417</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3679</v>
+        <v>-3.1015</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4683</v>
+        <v>-0.4402</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7411</v>
@@ -1386,13 +1386,13 @@
         <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.242</v>
+        <v>0.0524</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1643</v>
+        <v>0.1021</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0496</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1419,13 +1419,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3167</v>
+        <v>-5.9422</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.841</v>
+        <v>-5.8774</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5244</v>
+        <v>-0.0648</v>
       </c>
       <c r="G13" t="n">
         <v>-6.7736</v>
@@ -1464,13 +1464,13 @@
         <v>2.7774</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0868</v>
+        <v>0.2876</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3375</v>
+        <v>-0.374</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2508</v>
+        <v>0.6616</v>
       </c>
       <c r="V13" t="n">
         <v>0.9405</v>
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.037299999999999</v>
+        <v>-3.270299999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.266800000000001</v>
+        <v>-1.1357</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7704</v>
+        <v>-2.134499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-11.7693</v>
@@ -1542,16 +1542,16 @@
         <v>19.4416</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1322</v>
+        <v>0.6349</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.099299999999999</v>
+        <v>-0.9683999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9672000000000001</v>
+        <v>1.6031</v>
       </c>
       <c r="V14" t="n">
-        <v>3.301300000000002</v>
+        <v>3.301300000000001</v>
       </c>
       <c r="W14" t="n">
         <v>10.7156</v>
@@ -1575,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.3809</v>
+        <v>7.3971</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6999</v>
+        <v>5.4959</v>
       </c>
       <c r="F15" t="n">
-        <v>1.681</v>
+        <v>1.9012</v>
       </c>
       <c r="G15" t="n">
         <v>5.2584</v>
@@ -1620,13 +1620,13 @@
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2431</v>
+        <v>0.2593</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1813</v>
+        <v>-0.3853</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4244</v>
+        <v>0.6446</v>
       </c>
       <c r="V15" t="n">
         <v>1.0858</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2416</v>
+        <v>5.0162</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0676</v>
+        <v>2.3737</v>
       </c>
       <c r="F16" t="n">
-        <v>2.174</v>
+        <v>2.6425</v>
       </c>
       <c r="G16" t="n">
         <v>1.6354</v>
@@ -1698,13 +1698,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7987</v>
+        <v>-0.0241</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6744</v>
+        <v>-0.3684</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1242</v>
+        <v>0.3443</v>
       </c>
       <c r="V16" t="n">
         <v>2.4129</v>
@@ -1731,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6463</v>
+        <v>4.5747</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3777</v>
+        <v>3.7858</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2686</v>
+        <v>0.7889</v>
       </c>
       <c r="G17" t="n">
         <v>3.8565</v>
@@ -1776,13 +1776,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.407</v>
+        <v>0.5215</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5554</v>
+        <v>-0.1472</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1484</v>
+        <v>0.6687</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7952</v>
@@ -1809,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1451</v>
+        <v>3.9758</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7571</v>
+        <v>2.0632</v>
       </c>
       <c r="F18" t="n">
-        <v>1.388</v>
+        <v>1.9126</v>
       </c>
       <c r="G18" t="n">
         <v>3.3352</v>
@@ -1854,13 +1854,13 @@
         <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2171</v>
+        <v>0.6136</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.68</v>
+        <v>-0.374</v>
       </c>
       <c r="U18" t="n">
-        <v>0.463</v>
+        <v>0.9875</v>
       </c>
       <c r="V18" t="n">
         <v>1.8125</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7691</v>
+        <v>1.8475</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4741</v>
+        <v>2.066</v>
       </c>
       <c r="F19" t="n">
-        <v>0.295</v>
+        <v>-0.2185</v>
       </c>
       <c r="G19" t="n">
         <v>4.5949</v>
@@ -1932,13 +1932,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8648</v>
+        <v>-0.0567</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0056</v>
+        <v>-0.4137</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8704</v>
+        <v>0.357</v>
       </c>
       <c r="V19" t="n">
         <v>-3.0874</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. NGOMO MIFUMU</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5722</v>
+        <v>-0.6138</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4807</v>
+        <v>-0.1741</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9085</v>
+        <v>-0.4398</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8794</v>
+        <v>0.0074</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2237</v>
+        <v>0.4582</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6557</v>
+        <v>-0.4508</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3922</v>
+        <v>0.1206</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4319</v>
+        <v>0.0403</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9603</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4872</v>
+        <v>-0.1133</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.4179</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3046</v>
+        <v>-0.5312</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2133</v>
+        <v>-0.4067</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4148</v>
+        <v>-0.2947</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7985</v>
+        <v>-0.112</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4826</v>
+        <v>-1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9899</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>O. NGOMO MIFUMU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2303</v>
+        <v>-1.8909</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3781</v>
+        <v>-3.0111</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8521</v>
+        <v>1.1202</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0074</v>
+        <v>-2.8794</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4582</v>
+        <v>-1.2237</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4508</v>
+        <v>-1.6557</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1206</v>
+        <v>-2.3922</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0403</v>
+        <v>-0.4319</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0803</v>
+        <v>-1.9603</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1133</v>
+        <v>-0.4872</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4179</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5312</v>
+        <v>0.3046</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9919</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0231</v>
+        <v>1.8946</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4988</v>
+        <v>0.8844</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5243</v>
+        <v>1.0102</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>0.4826</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-0.9899</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7847</v>
+        <v>-4.4482</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7476</v>
+        <v>-5.9314</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9629</v>
+        <v>1.4832</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0234</v>
@@ -2166,13 +2166,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2005</v>
+        <v>0.136</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2469</v>
+        <v>-0.4307</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0464</v>
+        <v>0.5667</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3866</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1114</v>
+        <v>-6.6532</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7143</v>
+        <v>-2.6122</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3972</v>
+        <v>-4.0409</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5822</v>
@@ -2244,13 +2244,13 @@
         <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1082</v>
+        <v>0.35</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1303</v>
+        <v>-0.0283</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0221</v>
+        <v>0.3783</v>
       </c>
       <c r="V23" t="n">
         <v>-3.6194</v>
@@ -2277,13 +2277,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.484399999999999</v>
+        <v>9.2052</v>
       </c>
       <c r="E24" t="n">
-        <v>4.0557</v>
+        <v>4.055800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4287</v>
+        <v>5.149400000000001</v>
       </c>
       <c r="G24" t="n">
         <v>11.2028</v>
@@ -2322,13 +2322,13 @@
         <v>14.8788</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5666000000000003</v>
+        <v>3.2875</v>
       </c>
       <c r="T24" t="n">
         <v>-1.5579</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1247</v>
+        <v>4.845300000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-3.3013</v>
